--- a/framework-pdfs/PFWP BRISK.xlsx
+++ b/framework-pdfs/PFWP BRISK.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Martin/Documents/0 Punkfrog/06 Quality/Templates/13 Operations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02763435-7220-0B44-9406-94F457AEDE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD935128-33DC-FE44-9EA4-97EA6F853C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-13960" yWindow="-23140" windowWidth="28920" windowHeight="21880" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -439,10 +439,6 @@
 Mathematically, probability is a value between 0 and 1. The drop-down menu shows 10% to 90%, because 0% means never, and 100% means the risk event is actually a fact, so these two values are excluded.</t>
   </si>
   <si>
-    <t>PF/O-26:004
-2026-03-06 version 2.0.1</t>
-  </si>
-  <si>
     <t>• Record the assumptions and methods used to estimate the financial impact under REMARKS, so that these can be challenged and improved.
 • Express IMPA€T in the most relevant currency, and modify this in the heading.</t>
   </si>
@@ -455,6 +451,10 @@
   <si>
     <t>Use the Monte Carlo method, or is available EMV from the BRISK register. The PM could present the main risks that should be addressed when negotiating the budget with upper management.
 The costs for pre-emptive measures are already included in the main project budget, and hopefully obviate the need to use the Contingency Reserve.</t>
+  </si>
+  <si>
+    <t>PF/O-26:004
+2026-03-06 version 2.0.0</t>
   </si>
 </sst>
 </file>
@@ -1136,15 +1136,24 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1159,15 +1168,6 @@
     </xf>
     <xf numFmtId="0" fontId="20" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1513,16 +1513,16 @@
       </c>
       <c r="B1" s="8"/>
       <c r="D1" s="15" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="75" customFormat="1" ht="27" customHeight="1">
-      <c r="A2" s="76" t="s">
+      <c r="A2" s="81" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="76"/>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
     </row>
     <row r="3" spans="1:4" s="13" customFormat="1" ht="27">
       <c r="A3" s="11" t="s">
@@ -1532,28 +1532,28 @@
       <c r="D3" s="12"/>
     </row>
     <row r="4" spans="1:4" s="13" customFormat="1" ht="19">
-      <c r="A4" s="79" t="s">
+      <c r="A4" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="B4" s="79"/>
-      <c r="C4" s="79"/>
-      <c r="D4" s="79"/>
+      <c r="B4" s="82"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
     </row>
     <row r="5" spans="1:4" ht="40" customHeight="1">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="83" t="s">
         <v>80</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="80"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
     </row>
     <row r="6" spans="1:4" ht="57" customHeight="1">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="83" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="80"/>
-      <c r="C6" s="80"/>
-      <c r="D6" s="80"/>
+      <c r="B6" s="83"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="83"/>
     </row>
     <row r="7" spans="1:4" s="13" customFormat="1" ht="27">
       <c r="A7" s="11" t="s">
@@ -1563,20 +1563,20 @@
       <c r="D7" s="12"/>
     </row>
     <row r="8" spans="1:4" s="13" customFormat="1" ht="19">
-      <c r="A8" s="80" t="s">
+      <c r="A8" s="83" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="80"/>
-      <c r="C8" s="80"/>
-      <c r="D8" s="80"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="83"/>
+      <c r="D8" s="83"/>
     </row>
     <row r="9" spans="1:4" s="13" customFormat="1" ht="19">
-      <c r="A9" s="80" t="s">
+      <c r="A9" s="83" t="s">
         <v>82</v>
       </c>
-      <c r="B9" s="80"/>
-      <c r="C9" s="80"/>
-      <c r="D9" s="80"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="83"/>
+      <c r="D9" s="83"/>
     </row>
     <row r="10" spans="1:4" s="13" customFormat="1" ht="6" customHeight="1">
       <c r="A10" s="22"/>
@@ -1591,100 +1591,100 @@
       <c r="B11" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="85" t="s">
+      <c r="C11" s="79" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="86"/>
+      <c r="D11" s="80"/>
     </row>
     <row r="12" spans="1:4" s="5" customFormat="1" ht="69" customHeight="1">
-      <c r="A12" s="81" t="str">
+      <c r="A12" s="84" t="str">
         <f>'BRISK Register'!C2</f>
         <v>MAJOR RISK</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C12" s="77" t="s">
+      <c r="C12" s="76" t="s">
         <v>46</v>
       </c>
-      <c r="D12" s="78"/>
+      <c r="D12" s="77"/>
     </row>
     <row r="13" spans="1:4" s="5" customFormat="1" ht="53" customHeight="1">
-      <c r="A13" s="82"/>
+      <c r="A13" s="85"/>
       <c r="B13" s="59" t="str">
         <f>'BRISK Register'!C3</f>
         <v>TECHNICAL</v>
       </c>
-      <c r="C13" s="77" t="s">
+      <c r="C13" s="76" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="78"/>
+      <c r="D13" s="77"/>
     </row>
     <row r="14" spans="1:4" s="5" customFormat="1" ht="18" customHeight="1">
-      <c r="A14" s="82"/>
+      <c r="A14" s="85"/>
       <c r="B14" s="59" t="str">
         <f>'BRISK Register'!C8</f>
         <v>PRODUCT / REQUIREMENTS</v>
       </c>
-      <c r="C14" s="77" t="s">
+      <c r="C14" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="78"/>
+      <c r="D14" s="77"/>
     </row>
     <row r="15" spans="1:4" s="5" customFormat="1" ht="37" customHeight="1">
-      <c r="A15" s="82"/>
+      <c r="A15" s="85"/>
       <c r="B15" s="59" t="str">
         <f>'BRISK Register'!C13</f>
         <v>PERSONNEL</v>
       </c>
-      <c r="C15" s="77" t="s">
+      <c r="C15" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="D15" s="78"/>
+      <c r="D15" s="77"/>
     </row>
     <row r="16" spans="1:4" s="5" customFormat="1" ht="52" customHeight="1">
-      <c r="A16" s="82"/>
+      <c r="A16" s="85"/>
       <c r="B16" s="59" t="str">
         <f>'BRISK Register'!C18</f>
         <v>ADMINISTRATION / MANAGEMENT</v>
       </c>
-      <c r="C16" s="77" t="s">
+      <c r="C16" s="76" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="78"/>
+      <c r="D16" s="77"/>
     </row>
     <row r="17" spans="1:17" s="5" customFormat="1" ht="18" customHeight="1">
-      <c r="A17" s="82"/>
+      <c r="A17" s="85"/>
       <c r="B17" s="59" t="str">
         <f>'BRISK Register'!C23</f>
         <v>SUPPLIER / EXTERNAL</v>
       </c>
-      <c r="C17" s="77" t="s">
+      <c r="C17" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="D17" s="78"/>
+      <c r="D17" s="77"/>
     </row>
     <row r="18" spans="1:17" s="5" customFormat="1" ht="18" customHeight="1">
-      <c r="A18" s="82"/>
+      <c r="A18" s="85"/>
       <c r="B18" s="59" t="str">
         <f>'BRISK Register'!C28</f>
         <v>OPERATIONAL / DEPLOYMENT</v>
       </c>
-      <c r="C18" s="77" t="s">
+      <c r="C18" s="76" t="s">
         <v>72</v>
       </c>
-      <c r="D18" s="78"/>
+      <c r="D18" s="77"/>
     </row>
     <row r="19" spans="1:17" s="5" customFormat="1" ht="37" customHeight="1">
-      <c r="A19" s="83"/>
+      <c r="A19" s="86"/>
       <c r="B19" s="59" t="str">
         <f>'BRISK Register'!C33</f>
         <v>XXX</v>
       </c>
-      <c r="C19" s="77" t="s">
+      <c r="C19" s="76" t="s">
         <v>74</v>
       </c>
-      <c r="D19" s="78"/>
+      <c r="D19" s="77"/>
     </row>
     <row r="20" spans="1:17" s="5" customFormat="1" ht="120" customHeight="1">
       <c r="A20" s="71" t="str">
@@ -1694,10 +1694,10 @@
       <c r="B20" s="59" t="s">
         <v>98</v>
       </c>
-      <c r="C20" s="77" t="s">
+      <c r="C20" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="78"/>
+      <c r="D20" s="77"/>
     </row>
     <row r="21" spans="1:17" s="5" customFormat="1" ht="151" customHeight="1">
       <c r="A21" s="71" t="str">
@@ -1707,10 +1707,10 @@
       <c r="B21" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C21" s="77" t="s">
+      <c r="C21" s="76" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="78"/>
+      <c r="D21" s="77"/>
     </row>
     <row r="22" spans="1:17" s="5" customFormat="1" ht="71" customHeight="1">
       <c r="A22" s="71" t="str">
@@ -1720,10 +1720,10 @@
       <c r="B22" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="77" t="s">
+      <c r="C22" s="76" t="s">
         <v>75</v>
       </c>
-      <c r="D22" s="78"/>
+      <c r="D22" s="77"/>
     </row>
     <row r="23" spans="1:17" s="5" customFormat="1" ht="70" customHeight="1">
       <c r="A23" s="72" t="str">
@@ -1734,10 +1734,10 @@
       <c r="B23" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="C23" s="77" t="s">
-        <v>100</v>
-      </c>
-      <c r="D23" s="78"/>
+      <c r="C23" s="76" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" s="77"/>
       <c r="E23" s="61"/>
     </row>
     <row r="24" spans="1:17" s="5" customFormat="1" ht="104" customHeight="1">
@@ -1748,10 +1748,10 @@
       <c r="B24" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C24" s="77" t="s">
+      <c r="C24" s="76" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="78"/>
+      <c r="D24" s="77"/>
     </row>
     <row r="25" spans="1:17" s="5" customFormat="1" ht="54">
       <c r="A25" s="71" t="str">
@@ -1761,10 +1761,10 @@
       <c r="B25" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="C25" s="77" t="s">
+      <c r="C25" s="76" t="s">
         <v>96</v>
       </c>
-      <c r="D25" s="78"/>
+      <c r="D25" s="77"/>
       <c r="E25" s="61"/>
     </row>
     <row r="26" spans="1:17" s="5" customFormat="1" ht="53" customHeight="1">
@@ -1773,12 +1773,12 @@
         <v>CONTINGENCY PLAN</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="C26" s="77" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" s="76" t="s">
         <v>88</v>
       </c>
-      <c r="D26" s="78"/>
+      <c r="D26" s="77"/>
       <c r="E26" s="61"/>
     </row>
     <row r="28" spans="1:17" s="13" customFormat="1" ht="27">
@@ -1789,12 +1789,12 @@
       <c r="D28" s="12"/>
     </row>
     <row r="29" spans="1:17" ht="42" customHeight="1">
-      <c r="A29" s="84" t="s">
-        <v>102</v>
-      </c>
-      <c r="B29" s="84"/>
-      <c r="C29" s="84"/>
-      <c r="D29" s="84"/>
+      <c r="A29" s="78" t="s">
+        <v>101</v>
+      </c>
+      <c r="B29" s="78"/>
+      <c r="C29" s="78"/>
+      <c r="D29" s="78"/>
       <c r="E29" s="19"/>
       <c r="F29" s="19"/>
       <c r="G29" s="19"/>
@@ -1847,7 +1847,7 @@
         <v>92</v>
       </c>
       <c r="D31" s="74" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="5" customFormat="1" ht="152" customHeight="1">
@@ -2125,6 +2125,14 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A12:A19"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="C26:D26"/>
     <mergeCell ref="A29:D29"/>
     <mergeCell ref="C11:D11"/>
@@ -2141,14 +2149,6 @@
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="C23:D23"/>
     <mergeCell ref="C24:D24"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A12:A19"/>
-    <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A6:D6"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
